--- a/output/topology_excel/1398.xlsx
+++ b/output/topology_excel/1398.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>249</v>
+        <v>417</v>
       </c>
       <c r="F27" t="n">
-        <v>150</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>461</v>
+        <v>124</v>
       </c>
       <c r="F28" t="n">
-        <v>330</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>633</v>
+        <v>135</v>
       </c>
       <c r="F29" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,18 +1092,18 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F30" t="n">
-        <v>116</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,18 +1114,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="F31" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="F32" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>314</v>
+        <v>149</v>
       </c>
       <c r="F33" t="n">
-        <v>50</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,18 +1180,18 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>685</v>
+        <v>123</v>
       </c>
       <c r="F34" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,19 +1202,19 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="F35" t="n">
-        <v>40</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="n">
         <v>2</v>
       </c>
-      <c r="B36" t="n">
-        <v>13</v>
-      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1224,10 +1224,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>547</v>
+        <v>296</v>
       </c>
       <c r="F36" t="n">
-        <v>209</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
@@ -1235,7 +1235,7 @@
         <v>2</v>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="F37" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>71</v>
+        <v>461</v>
       </c>
       <c r="F38" t="n">
-        <v>23</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>135</v>
+        <v>249</v>
       </c>
       <c r="F39" t="n">
-        <v>47</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B40" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>88</v>
+        <v>633</v>
       </c>
       <c r="F40" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B41" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,40 +1334,40 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="F41" t="n">
-        <v>112</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B42" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>43</v>
+      </c>
+      <c r="F42" t="n">
         <v>20</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="n">
-        <v>123</v>
-      </c>
-      <c r="F42" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B43" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>474</v>
+        <v>314</v>
       </c>
       <c r="F43" t="n">
-        <v>187</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B44" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,18 +1400,18 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>296</v>
+        <v>685</v>
       </c>
       <c r="F44" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>633</v>
+        <v>485</v>
       </c>
       <c r="F45" t="n">
         <v>40</v>
@@ -1433,7 +1433,7 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,18 +1444,18 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>444</v>
+        <v>504</v>
       </c>
       <c r="F46" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B47" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B48" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,18 +1488,18 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,18 +1510,18 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>118</v>
+        <v>633</v>
       </c>
       <c r="F49" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B50" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,10 +1532,10 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>103</v>
+        <v>444</v>
       </c>
       <c r="F50" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
@@ -1543,7 +1543,7 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,10 +1554,10 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F51" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
@@ -1565,29 +1565,29 @@
         <v>10</v>
       </c>
       <c r="B52" t="n">
+        <v>15</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>43</v>
+      </c>
+      <c r="F52" t="n">
         <v>11</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" t="n">
-        <v>607</v>
-      </c>
-      <c r="F52" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B53" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,18 +1598,18 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="F53" t="n">
-        <v>109</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B54" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>367</v>
+        <v>103</v>
       </c>
       <c r="F54" t="n">
         <v>50</v>
@@ -1631,7 +1631,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>591</v>
+        <v>114</v>
       </c>
       <c r="F55" t="n">
         <v>13</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B56" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>228</v>
+        <v>607</v>
       </c>
       <c r="F56" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
@@ -1675,7 +1675,7 @@
         <v>12</v>
       </c>
       <c r="B57" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,15 +1686,15 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>592</v>
+        <v>127</v>
       </c>
       <c r="F57" t="n">
-        <v>13</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B58" t="n">
         <v>17</v>
@@ -1708,10 +1708,10 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>134</v>
+        <v>367</v>
       </c>
       <c r="F58" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -1719,7 +1719,7 @@
         <v>13</v>
       </c>
       <c r="B59" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>111</v>
+        <v>591</v>
       </c>
       <c r="F59" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
@@ -1741,7 +1741,7 @@
         <v>13</v>
       </c>
       <c r="B60" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,10 +1752,10 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>147</v>
+        <v>228</v>
       </c>
       <c r="F60" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61">
@@ -1774,10 +1774,10 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>656</v>
+        <v>592</v>
       </c>
       <c r="F61" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -1785,7 +1785,7 @@
         <v>15</v>
       </c>
       <c r="B62" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,18 +1796,18 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="F62" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B63" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1818,18 +1818,18 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="F63" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B64" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1840,18 +1840,18 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="F64" t="n">
-        <v>15</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B65" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1862,18 +1862,18 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>97</v>
+        <v>656</v>
       </c>
       <c r="F65" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B66" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67">
@@ -1895,7 +1895,7 @@
         <v>19</v>
       </c>
       <c r="B67" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="F67" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
@@ -1917,7 +1917,7 @@
         <v>19</v>
       </c>
       <c r="B68" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1931,12 +1931,12 @@
         <v>88</v>
       </c>
       <c r="F68" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B69" t="n">
         <v>22</v>
@@ -1950,32 +1950,120 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="F69" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
+        <v>21</v>
+      </c>
+      <c r="B70" t="n">
         <v>22</v>
       </c>
-      <c r="B70" t="n">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>123</v>
+      </c>
+      <c r="F70" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>21</v>
+      </c>
+      <c r="B71" t="n">
+        <v>23</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>43</v>
+      </c>
+      <c r="F71" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>21</v>
+      </c>
+      <c r="B72" t="n">
         <v>24</v>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" t="n">
-        <v>188</v>
-      </c>
-      <c r="F70" t="n">
-        <v>41</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>88</v>
+      </c>
+      <c r="F72" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>23</v>
+      </c>
+      <c r="B73" t="n">
+        <v>24</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>63</v>
+      </c>
+      <c r="F73" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>142</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/1398.xlsx
+++ b/output/topology_excel/1398.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Length_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Width_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Length_6</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Width_6</t>
         </is>
       </c>
     </row>
@@ -481,6 +531,16 @@
       <c r="F2" t="n">
         <v>12</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +563,16 @@
       <c r="F3" t="n">
         <v>16</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -517,7 +587,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>133</v>
@@ -525,6 +595,16 @@
       <c r="F4" t="n">
         <v>30</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +627,16 @@
       <c r="F5" t="n">
         <v>14</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +659,16 @@
       <c r="F6" t="n">
         <v>15</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +691,16 @@
       <c r="F7" t="n">
         <v>13</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +723,16 @@
       <c r="F8" t="n">
         <v>13</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -627,7 +747,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>238</v>
@@ -635,6 +755,16 @@
       <c r="F9" t="n">
         <v>26</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +787,16 @@
       <c r="F10" t="n">
         <v>13</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +819,16 @@
       <c r="F11" t="n">
         <v>23</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +851,16 @@
       <c r="F12" t="n">
         <v>13</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +883,16 @@
       <c r="F13" t="n">
         <v>13</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +915,16 @@
       <c r="F14" t="n">
         <v>47</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +947,16 @@
       <c r="F15" t="n">
         <v>13</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +979,16 @@
       <c r="F16" t="n">
         <v>13</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +1011,16 @@
       <c r="F17" t="n">
         <v>11</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +1043,16 @@
       <c r="F18" t="n">
         <v>15</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +1075,16 @@
       <c r="F19" t="n">
         <v>11</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +1107,16 @@
       <c r="F20" t="n">
         <v>15</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +1139,16 @@
       <c r="F21" t="n">
         <v>42</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +1171,16 @@
       <c r="F22" t="n">
         <v>45</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -935,7 +1195,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>396</v>
@@ -943,6 +1203,16 @@
       <c r="F23" t="n">
         <v>32</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1235,16 @@
       <c r="F24" t="n">
         <v>13</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1267,16 @@
       <c r="F25" t="n">
         <v>13</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1299,16 @@
       <c r="F26" t="n">
         <v>13</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1331,16 @@
       <c r="F27" t="n">
         <v>39</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1045,13 +1355,43 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="F28" t="n">
-        <v>116</v>
+        <v>16</v>
+      </c>
+      <c r="G28" t="n">
+        <v>39</v>
+      </c>
+      <c r="H28" t="n">
+        <v>16</v>
+      </c>
+      <c r="I28" t="n">
+        <v>84</v>
+      </c>
+      <c r="J28" t="n">
+        <v>16</v>
+      </c>
+      <c r="K28" t="n">
+        <v>43</v>
+      </c>
+      <c r="L28" t="n">
+        <v>16</v>
+      </c>
+      <c r="M28" t="n">
+        <v>29</v>
+      </c>
+      <c r="N28" t="n">
+        <v>16</v>
+      </c>
+      <c r="O28" t="n">
+        <v>92</v>
+      </c>
+      <c r="P28" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -1067,14 +1407,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G29" t="n">
+        <v>24</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1089,14 +1443,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="F30" t="n">
-        <v>47</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G30" t="n">
+        <v>120</v>
+      </c>
+      <c r="H30" t="n">
+        <v>15</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1487,16 @@
       <c r="F31" t="n">
         <v>43</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1519,16 @@
       <c r="F32" t="n">
         <v>15</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1155,14 +1543,28 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="F33" t="n">
-        <v>112</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G33" t="n">
+        <v>134</v>
+      </c>
+      <c r="H33" t="n">
+        <v>15</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1587,16 @@
       <c r="F34" t="n">
         <v>15</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1199,14 +1611,28 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>474</v>
+        <v>433</v>
       </c>
       <c r="F35" t="n">
-        <v>187</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G35" t="n">
+        <v>145</v>
+      </c>
+      <c r="H35" t="n">
+        <v>41</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1221,14 +1647,28 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>296</v>
+        <v>30</v>
       </c>
       <c r="F36" t="n">
-        <v>46</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G36" t="n">
+        <v>280</v>
+      </c>
+      <c r="H36" t="n">
+        <v>16</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1691,16 @@
       <c r="F37" t="n">
         <v>41</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1265,14 +1715,28 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="F38" t="n">
-        <v>291</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G38" t="n">
+        <v>276</v>
+      </c>
+      <c r="H38" t="n">
+        <v>15</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1287,14 +1751,32 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F39" t="n">
-        <v>150</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G39" t="n">
+        <v>223</v>
+      </c>
+      <c r="H39" t="n">
+        <v>14</v>
+      </c>
+      <c r="I39" t="n">
+        <v>124</v>
+      </c>
+      <c r="J39" t="n">
+        <v>12</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1309,14 +1791,28 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>633</v>
+        <v>416</v>
       </c>
       <c r="F40" t="n">
         <v>14</v>
       </c>
+      <c r="G40" t="n">
+        <v>203</v>
+      </c>
+      <c r="H40" t="n">
+        <v>14</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1337,8 +1833,18 @@
         <v>114</v>
       </c>
       <c r="F41" t="n">
-        <v>52</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1867,16 @@
       <c r="F42" t="n">
         <v>20</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1899,16 @@
       <c r="F43" t="n">
         <v>50</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1403,8 +1929,18 @@
         <v>685</v>
       </c>
       <c r="F44" t="n">
-        <v>44</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1425,8 +1961,18 @@
         <v>485</v>
       </c>
       <c r="F45" t="n">
-        <v>40</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1447,8 +1993,18 @@
         <v>504</v>
       </c>
       <c r="F46" t="n">
-        <v>43</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +2027,16 @@
       <c r="F47" t="n">
         <v>13</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +2059,16 @@
       <c r="F48" t="n">
         <v>23</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1513,8 +2089,18 @@
         <v>633</v>
       </c>
       <c r="F49" t="n">
-        <v>40</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +2123,16 @@
       <c r="F50" t="n">
         <v>23</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +2155,16 @@
       <c r="F51" t="n">
         <v>15</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +2187,16 @@
       <c r="F52" t="n">
         <v>11</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +2219,16 @@
       <c r="F53" t="n">
         <v>13</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +2251,16 @@
       <c r="F54" t="n">
         <v>50</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +2283,16 @@
       <c r="F55" t="n">
         <v>13</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1669,6 +2315,16 @@
       <c r="F56" t="n">
         <v>13</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1683,14 +2339,28 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="F57" t="n">
-        <v>109</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G57" t="n">
+        <v>114</v>
+      </c>
+      <c r="H57" t="n">
+        <v>13</v>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +2383,16 @@
       <c r="F58" t="n">
         <v>50</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1735,6 +2415,16 @@
       <c r="F59" t="n">
         <v>13</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +2447,16 @@
       <c r="F60" t="n">
         <v>45</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +2479,16 @@
       <c r="F61" t="n">
         <v>13</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1801,6 +2511,16 @@
       <c r="F62" t="n">
         <v>43</v>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1823,6 +2543,16 @@
       <c r="F63" t="n">
         <v>43</v>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1837,14 +2567,28 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="F64" t="n">
-        <v>82</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G64" t="n">
+        <v>134</v>
+      </c>
+      <c r="H64" t="n">
+        <v>13</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1867,6 +2611,16 @@
       <c r="F65" t="n">
         <v>47</v>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1889,6 +2643,16 @@
       <c r="F66" t="n">
         <v>50</v>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1911,6 +2675,16 @@
       <c r="F67" t="n">
         <v>11</v>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1933,6 +2707,16 @@
       <c r="F68" t="n">
         <v>15</v>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1955,6 +2739,16 @@
       <c r="F69" t="n">
         <v>15</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1977,6 +2771,16 @@
       <c r="F70" t="n">
         <v>11</v>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1999,6 +2803,16 @@
       <c r="F71" t="n">
         <v>29</v>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2021,6 +2835,16 @@
       <c r="F72" t="n">
         <v>42</v>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2043,6 +2867,16 @@
       <c r="F73" t="n">
         <v>43</v>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2065,6 +2899,16 @@
       <c r="F74" t="n">
         <v>1</v>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
